--- a/Week_03/fiscal_data.xlsx
+++ b/Week_03/fiscal_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kayku\ZHAW\DataAnalytics\Excercises\data_analytics\Week_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A2F7F2-E068-484F-8B66-A6E34BAA244F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB17EA4B-D04E-470F-A6A7-D06E2B97F84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13354,7 +13354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -13367,8 +13367,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -13684,12 +13685,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
       <c r="E1" s="1">
         <v>27598</v>
       </c>
@@ -53299,11 +53300,11 @@
     </row>
     <row r="2205" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2206" s="11" t="s">
+      <c r="A2206" s="10" t="s">
         <v>4403</v>
       </c>
-      <c r="B2206" s="11"/>
-      <c r="C2206" s="11"/>
+      <c r="B2206" s="10"/>
+      <c r="C2206" s="10"/>
       <c r="D2206" s="7" t="s">
         <v>4404</v>
       </c>
@@ -53312,11 +53313,11 @@
       </c>
     </row>
     <row r="2207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2207" s="11" t="s">
+      <c r="A2207" s="10" t="s">
         <v>4406</v>
       </c>
-      <c r="B2207" s="11"/>
-      <c r="C2207" s="11"/>
+      <c r="B2207" s="10"/>
+      <c r="C2207" s="10"/>
       <c r="D2207" s="7" t="s">
         <v>4407</v>
       </c>
@@ -53325,68 +53326,67 @@
       </c>
     </row>
     <row r="2209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2209" s="11" t="s">
+      <c r="A2209" s="10" t="s">
         <v>4408</v>
       </c>
-      <c r="B2209" s="11"/>
-      <c r="C2209" s="11"/>
-      <c r="D2209" s="11"/>
-      <c r="E2209" s="11"/>
+      <c r="B2209" s="10"/>
+      <c r="C2209" s="10"/>
+      <c r="D2209" s="10"/>
+      <c r="E2209" s="10"/>
     </row>
     <row r="2211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2211" s="11" t="s">
+      <c r="A2211" s="10" t="s">
         <v>4409</v>
       </c>
-      <c r="B2211" s="11"/>
-      <c r="C2211" s="11"/>
-      <c r="D2211" s="11"/>
-      <c r="E2211" s="11"/>
+      <c r="B2211" s="10"/>
+      <c r="C2211" s="10"/>
+      <c r="D2211" s="10"/>
+      <c r="E2211" s="10"/>
     </row>
     <row r="2212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2212" s="11" t="s">
+      <c r="A2212" s="10" t="s">
         <v>4410</v>
       </c>
-      <c r="B2212" s="11"/>
-      <c r="C2212" s="11"/>
-      <c r="D2212" s="11"/>
-      <c r="E2212" s="11"/>
+      <c r="B2212" s="10"/>
+      <c r="C2212" s="10"/>
+      <c r="D2212" s="10"/>
+      <c r="E2212" s="10"/>
     </row>
     <row r="2213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2213" s="11" t="s">
+      <c r="A2213" s="10" t="s">
         <v>4411</v>
       </c>
-      <c r="B2213" s="11"/>
-      <c r="C2213" s="11"/>
-      <c r="D2213" s="11"/>
-      <c r="E2213" s="11"/>
+      <c r="B2213" s="10"/>
+      <c r="C2213" s="10"/>
+      <c r="D2213" s="10"/>
+      <c r="E2213" s="10"/>
     </row>
     <row r="2214" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2215" s="11" t="s">
+      <c r="A2215" s="10" t="s">
         <v>4412</v>
       </c>
-      <c r="B2215" s="11"/>
-      <c r="C2215" s="11"/>
-      <c r="D2215" s="11"/>
-      <c r="E2215" s="11"/>
+      <c r="B2215" s="10"/>
+      <c r="C2215" s="10"/>
+      <c r="D2215" s="10"/>
+      <c r="E2215" s="10"/>
     </row>
     <row r="2216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2216" s="11" t="s">
+      <c r="A2216" s="10" t="s">
         <v>4413</v>
       </c>
-      <c r="B2216" s="11"/>
-      <c r="C2216" s="11"/>
-      <c r="D2216" s="11"/>
-      <c r="E2216" s="11"/>
+      <c r="B2216" s="10"/>
+      <c r="C2216" s="10"/>
+      <c r="D2216" s="10"/>
+      <c r="E2216" s="10"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A2212:E2212"/>
     <mergeCell ref="A2213:E2213"/>
     <mergeCell ref="A2215:E2215"/>
     <mergeCell ref="A2216:E2216"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2206:C2206"/>
     <mergeCell ref="A2207:C2207"/>
     <mergeCell ref="A2209:E2209"/>
